--- a/data/trans_orig/IP31B_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31B_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2933</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,9%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4984</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2321</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9084</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,32%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3787</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>10290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>8626</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12950</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>34,87%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10857</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6795</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>16005</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>24,65%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,43%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>36,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>19380</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26457</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>33,1%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6977</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4150</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10910</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>18,79%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>29,38%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>10727</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6970</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15662</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>24,36%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,83%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>35,57%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13160</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>19083</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13490</t>
+          <t>12397</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24933</t>
+          <t>23126</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6577</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3854</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10598</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10,38%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>28,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4680</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2164</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8940</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7900</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4365</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11765</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12580</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8248</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>14929</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14065</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10397</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18393</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>37,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>49,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12789</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8881</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17801</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>20,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>40,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17765</t>
+          <t>10889</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23003</t>
+          <t>15557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>38,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>30554</t>
+          <t>24953</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24318</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38286</t>
+          <t>30372</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>37137</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>37137</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>37137</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44036</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44036</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44036</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>40578</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>40578</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>44889</t>
+          <t>40578</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>77714</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>77714</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>88925</t>
+          <t>77714</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>25454</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18334</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33954</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>15082</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10078</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22218</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28308</t>
+          <t>12893</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20727</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37215</t>
+          <t>18147</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>43389</t>
+          <t>38348</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33429</t>
+          <t>29694</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54868</t>
+          <t>48687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69886</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>60247</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>79130</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>44,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>38,74%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>76028</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>66440</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>86400</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>47,84%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>41,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>54,37%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78543</t>
+          <t>71104</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68206</t>
+          <t>61791</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89915</t>
+          <t>79957</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>154571</t>
+          <t>140991</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139777</t>
+          <t>127170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169767</t>
+          <t>153890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>42152</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33211</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>50288</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>27,1%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>21,35%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>32,33%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>54514</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>44660</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>63669</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>34,31%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>28,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>40,07%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50370</t>
+          <t>49650</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40294</t>
+          <t>40882</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60603</t>
+          <t>59057</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>104885</t>
+          <t>91802</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90132</t>
+          <t>79476</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>118813</t>
+          <t>104445</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,73%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13252</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8785</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>19397</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6155</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3169</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10308</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>23212</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>12992</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32633</t>
+          <t>25595</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4791</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2362</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>10700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7129</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3942</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12305</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9969</t>
+          <t>10888</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>11052</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18161</t>
+          <t>17287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>155536</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>155536</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>155536</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>158908</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>158908</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>158908</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>179278</t>
+          <t>145177</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>179278</t>
+          <t>145177</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>179278</t>
+          <t>145177</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>338186</t>
+          <t>300714</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>338186</t>
+          <t>300714</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>338186</t>
+          <t>300714</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36948</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27925</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>49492</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,1%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>24,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>37432</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28472</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>47582</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>21,63%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>16,45%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>27,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>37423</t>
+          <t>40245</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27731</t>
+          <t>31164</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48985</t>
+          <t>50487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>74855</t>
+          <t>77193</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>63204</t>
+          <t>62631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89397</t>
+          <t>90915</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>100860</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>87098</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>114107</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>50,92%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>43,97%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,6%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>94240</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>83623</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>107181</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>54,45%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>48,32%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>61,93%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>108013</t>
+          <t>91999</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>92326</t>
+          <t>79337</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121661</t>
+          <t>103775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>202253</t>
+          <t>192859</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>184245</t>
+          <t>175444</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>220072</t>
+          <t>210075</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>51778</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>40941</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>62775</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>26,14%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>31,69%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>33764</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>24901</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>43179</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>19,51%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>14,39%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>24,95%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>56226</t>
+          <t>34639</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44885</t>
+          <t>26318</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>69545</t>
+          <t>44583</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>89990</t>
+          <t>86417</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76883</t>
+          <t>73656</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>106096</t>
+          <t>102193</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8508</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4668</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>14872</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>6816</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>3542</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>12635</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8726</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>15542</t>
+          <t>15431</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23504</t>
+          <t>23639</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -2536,107 +2536,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3614</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4916</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>4878</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>819</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4129</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>198094</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>198094</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>198094</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>210387</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>210387</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>210387</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>383459</t>
+          <t>372767</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>383459</t>
+          <t>372767</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>383459</t>
+          <t>372767</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>49372</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>38063</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>62804</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>16,9%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>13,03%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>21,49%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>64498</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>44803</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>79607</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>29,14%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>47817</t>
+          <t>68564</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36778</t>
+          <t>55705</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60621</t>
+          <t>82014</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>112315</t>
+          <t>117936</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>92698</t>
+          <t>101233</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132878</t>
+          <t>136604</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>25,0%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>165091</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>146750</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>183611</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>56,5%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>50,22%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>62,83%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>126351</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>87532</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>147589</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>46,25%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,04%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>54,03%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>169433</t>
+          <t>130302</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>148785</t>
+          <t>115914</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188088</t>
+          <t>144695</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>295784</t>
+          <t>295392</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248707</t>
+          <t>271491</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>327669</t>
+          <t>318207</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>65690</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>50875</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>83600</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>22,48%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>17,41%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>73126</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>47644</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>137422</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>26,77%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>17,44%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>50,3%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>74645</t>
+          <t>50756</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56863</t>
+          <t>39355</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>94499</t>
+          <t>62162</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>147771</t>
+          <t>116446</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>117391</t>
+          <t>97582</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>222600</t>
+          <t>137942</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>8697</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>15510</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>31329</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>11,47%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>463</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>10732</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39147</t>
+          <t>18337</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3371</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>10287</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2191</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2492</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>6664</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>8643</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3500</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>10772</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2096</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13620</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>273183</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>273183</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>273183</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>254149</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>254149</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>254149</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>578182</t>
+          <t>546370</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>578182</t>
+          <t>546370</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>578182</t>
+          <t>546370</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>112666</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>95658</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>130745</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>121996</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>100409</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>140216</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>18,79%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>21,6%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>115285</t>
+          <t>126614</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>98810</t>
+          <t>109025</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>134867</t>
+          <t>144966</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>239281</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>212258</t>
+          <t>213495</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>266073</t>
+          <t>264840</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>344463</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>319036</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>371426</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>50,43%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>46,71%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>54,38%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>307476</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>265085</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>333648</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>47,36%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>40,83%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>365120</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>337665</t>
+          <t>282669</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>395340</t>
+          <t>326544</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>672595</t>
+          <t>648622</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>620907</t>
+          <t>613763</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>712488</t>
+          <t>686937</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>166597</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>146588</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>189356</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>24,39%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>27,72%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>172131</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>144335</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>240155</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>36,99%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>189597</t>
+          <t>145143</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>165196</t>
+          <t>128779</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>217037</t>
+          <t>163508</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>361728</t>
+          <t>311740</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>325266</t>
+          <t>286448</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>432378</t>
+          <t>341675</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>37035</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>28583</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>48799</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>24669</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>16092</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>47211</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>43287</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32460</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>55268</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>67956</t>
+          <t>55186</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>53014</t>
+          <t>43681</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>91551</t>
+          <t>67970</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>22227</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>15446</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>30452</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>22927</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>16404</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>32428</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18904</t>
+          <t>14809</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>28927</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>42736</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>38916</t>
+          <t>34292</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>61916</t>
+          <t>55663</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>908</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
